--- a/data/processed/DGE_Revenue_Forecast_XGBoost_2026.xlsx
+++ b/data/processed/DGE_Revenue_Forecast_XGBoost_2026.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2149267.75</v>
+        <v>2085386.75</v>
       </c>
     </row>
     <row r="4">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" s="8" t="n">
-        <v>2358887.25</v>
+        <v>2570691</v>
       </c>
     </row>
     <row r="5">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2412206.75</v>
+        <v>2649504.25</v>
       </c>
     </row>
     <row r="6">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>2034275.75</v>
+        <v>2446111</v>
       </c>
     </row>
     <row r="7">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2266433</v>
+        <v>2271000.75</v>
       </c>
     </row>
     <row r="8">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>2021999.38</v>
+        <v>2491056.5</v>
       </c>
     </row>
     <row r="9">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1874729.38</v>
+        <v>2092556.25</v>
       </c>
     </row>
     <row r="10">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1990016.88</v>
+        <v>2183507.75</v>
       </c>
     </row>
     <row r="11">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1817860.12</v>
+        <v>2337603.5</v>
       </c>
     </row>
     <row r="12">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>1823820.88</v>
+        <v>2118988.75</v>
       </c>
     </row>
     <row r="13">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1823820.88</v>
+        <v>2071760.88</v>
       </c>
     </row>
     <row r="14">
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>1442057.88</v>
+        <v>1791618.38</v>
       </c>
     </row>
     <row r="15">
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>24015375.88</v>
+        <v>27109785.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>2025 Actuals (reference)  |  YoY: -20.3%</t>
+          <t>2025 Actuals (reference)  |  YoY: -10.1%</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
@@ -866,11 +866,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -957,55 +957,79 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>XGBoost Regressor – trained on Apr 2023 to Dec 2025 (33 months)</t>
+          <t>XGBoost Regressor – trained on Apr 2023 to Dec 2025 (33 months, 23 features)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Rolling one-step-ahead forecast; each prediction feeds next month's revenue lags</t>
+          <t>US macro lags (DGORDER, INDPRO), calendar, revenue AR/rolling</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Macro inputs</t>
+          <t>DE macro</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Carry-forward of Dec 2025 values from Jan 2026 onward (US data ends Dec 2025)</t>
+          <t>Excluded – no causal pathway from DE domestic orders to US customer revenue</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>B1/B2</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>NOT subtracted – this is gross B3. Net B3 = Gross B3 - (B1 + B2) in SAC</t>
+          <t>Rolling one-step-ahead; each prediction feeds next month's revenue lags</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>Macro inputs</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Carry-forward of Dec 2025 values from Jan 2026 onward</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>B1/B2</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>NOT subtracted – gross B3. Net B3 = Gross B3 - (B1+B2) in SAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
           <t>Limitation</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Synthetic data basis – absolute values demonstrate methodology, not calibrated forecast</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Synthetic data basis – absolute values demonstrate methodology</t>
         </is>
       </c>
     </row>
